--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4762BFB-BD8D-4863-839F-3427842A5FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3C736D-3B65-4E89-96DC-018A2618119E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Links</t>
   </si>
   <si>
-    <t xml:space="preserve"> Hans Ehm, Abdelgafar Ismail, Diallo Fadila, Excellence program Students , Botho Schanze</t>
-  </si>
-  <si>
     <t>Name(s) of responsible(s)</t>
   </si>
   <si>
@@ -86,12 +83,6 @@
     <t>Info</t>
   </si>
   <si>
-    <t>Fist session Jf , presentation</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -123,6 +114,93 @@
   </si>
   <si>
     <t>17.07.2026</t>
+  </si>
+  <si>
+    <t>Kick off of the Excellence program  Presentation of the Timeline</t>
+  </si>
+  <si>
+    <t>Abdo, Tim, Botho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Info </t>
+  </si>
+  <si>
+    <t>Abdo</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Plants</t>
+  </si>
+  <si>
+    <t>Esther</t>
+  </si>
+  <si>
+    <t>A/I</t>
+  </si>
+  <si>
+    <t>Water Supply</t>
+  </si>
+  <si>
+    <t>Phares</t>
+  </si>
+  <si>
+    <t>Product Transformation</t>
+  </si>
+  <si>
+    <t>Abdoul</t>
+  </si>
+  <si>
+    <t>Crop storage</t>
+  </si>
+  <si>
+    <t>Christelle</t>
+  </si>
+  <si>
+    <t>Energy Supply</t>
+  </si>
+  <si>
+    <t>Aida</t>
+  </si>
+  <si>
+    <t>Visitor Management</t>
+  </si>
+  <si>
+    <t>Alix</t>
+  </si>
+  <si>
+    <t>Fencing and security</t>
+  </si>
+  <si>
+    <t>Filomene</t>
+  </si>
+  <si>
+    <t>Machinery</t>
+  </si>
+  <si>
+    <t>Jean-Louis</t>
+  </si>
+  <si>
+    <t>Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Marieta</t>
+  </si>
+  <si>
+    <t>‒Study the sustainable farm from last year
+‒Use it as foundation for the new project
+‒Everyone focus on his task with possibility to brainstorm together as a team 
+‒Next week: summarize what you worked on during the week and update your homepage</t>
+  </si>
+  <si>
+    <t>Students</t>
+  </si>
+  <si>
+    <t>Tasks distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hans Ehm, Abdelgafar Ismail, Excellence program Students , Botho Schanze, Tim , Hans ,  Wilfried , Ana</t>
   </si>
 </sst>
 </file>
@@ -292,7 +370,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -357,6 +435,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1205,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -1271,16 +1361,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C4" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>11</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>12</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="13"/>
@@ -1288,16 +1378,16 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="C5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>15</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>16</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>6</v>
@@ -1317,20 +1407,271 @@
         <v>1</v>
       </c>
       <c r="B6" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="1"/>
       <c r="G6" s="18"/>
       <c r="H6" s="19"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="24">
+        <v>2</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="24">
+        <v>3</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="24">
+        <v>4</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="24">
+        <v>5</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="24">
+        <v>6</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="24">
+        <v>7</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="24">
+        <v>8</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="24">
+        <v>9</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="24">
+        <v>10</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="24">
+        <v>11</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+    </row>
+    <row r="17" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+      <c r="A17" s="24">
+        <v>12</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="25"/>
+      <c r="F17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="23"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="23"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="23"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1350,7 +1691,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -1371,7 +1712,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -1383,34 +1724,34 @@
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1537,18 +1878,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1568,18 +1909,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3C736D-3B65-4E89-96DC-018A2618119E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7AAB18-59B2-4688-A91A-8F770B44DA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="71">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -201,6 +201,73 @@
   </si>
   <si>
     <t xml:space="preserve"> Hans Ehm, Abdelgafar Ismail, Excellence program Students , Botho Schanze, Tim , Hans ,  Wilfried , Ana</t>
+  </si>
+  <si>
+    <t>24.07.2026</t>
+  </si>
+  <si>
+    <t>Presentation</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>Feedback info</t>
+  </si>
+  <si>
+    <t>Christelle:
+Crops storage: thank you for the very good updates
+Good that you thought of the most important aspects of the storage
+Did you consider the storage capacity from previous year – and show a status of the capacity in the app</t>
+  </si>
+  <si>
+    <t>Mariata:
+Sales &amp; marketing: thank you for the very good updates
+Good job to research  into what is existing already this is called state of the art – I recommend it as best practice
+Please look at what are the challenges to create an app</t>
+  </si>
+  <si>
+    <t>Tania:
+Face recognition: thank you for the very good updates
+Good job to start with improving and enhancing the previous work – also recommend it as best practive</t>
+  </si>
+  <si>
+    <t>Abdoul:
+Product transform: thank you for the very good updates
+Good job to study and reverse engineer previous solution – data model is very good step as well – please share a screenshot of it next time
+Did you think of how the app should contain the most important aspects of product transformation</t>
+  </si>
+  <si>
+    <t>Ester:
+Plants: thank you for the very good updates
+Good job to review the previous work – do plausi check for the calculation in excel – thank you for fixing the error
+As next step I would recommend to list what are the important aspects of the plants app – you already did first step – think which aspects are needed for which partner downstream in the supply chain</t>
+  </si>
+  <si>
+    <t>Phares:
+Irrigation system: thank you for the very good updates
+Good job to research  into what is existing already this is called state of the art
+I would recommend to focus on designing the app to make more water saving planning</t>
+  </si>
+  <si>
+    <t>Jean-Louis:
+Equipment: thank you for the very good updates
+Good job to research  into what is existing already this is called state of the art
+One of the most important aspects of machine is utilization and maintenance I would recommend to include in the app</t>
+  </si>
+  <si>
+    <t>Aida:
+Not in the call</t>
+  </si>
+  <si>
+    <t>Alix:
+Not in the call</t>
+  </si>
+  <si>
+    <t>Hans and Abdo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hans Ehm, Abdelgafar Ismail, Excellence program Students , Botho Schanze, Tim , Hans ,  Wilfried , Ana….</t>
   </si>
 </sst>
 </file>
@@ -370,7 +437,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -430,23 +497,32 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1295,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -1307,16 +1383,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
@@ -1425,16 +1501,16 @@
       <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="24">
+      <c r="A7" s="21">
         <v>2</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E7" s="20" t="s">
@@ -1443,20 +1519,20 @@
       <c r="F7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="24">
+      <c r="A8" s="21">
         <v>3</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="20" t="s">
@@ -1465,20 +1541,20 @@
       <c r="F8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="24">
+      <c r="A9" s="21">
         <v>4</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="22" t="s">
         <v>37</v>
       </c>
       <c r="E9" s="20" t="s">
@@ -1487,20 +1563,20 @@
       <c r="F9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="24">
+      <c r="A10" s="21">
         <v>5</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="22" t="s">
         <v>39</v>
       </c>
       <c r="E10" s="20" t="s">
@@ -1509,20 +1585,20 @@
       <c r="F10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="24">
+      <c r="A11" s="21">
         <v>6</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="22" t="s">
         <v>41</v>
       </c>
       <c r="E11" s="20" t="s">
@@ -1531,20 +1607,20 @@
       <c r="F11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="24">
+      <c r="A12" s="21">
         <v>7</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="22" t="s">
         <v>43</v>
       </c>
       <c r="E12" s="20" t="s">
@@ -1553,20 +1629,20 @@
       <c r="F12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="24">
+      <c r="A13" s="21">
         <v>8</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="22" t="s">
         <v>45</v>
       </c>
       <c r="E13" s="20" t="s">
@@ -1575,20 +1651,20 @@
       <c r="F13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="24">
+      <c r="A14" s="21">
         <v>9</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="22" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="20" t="s">
@@ -1597,20 +1673,20 @@
       <c r="F14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="24">
+      <c r="A15" s="21">
         <v>10</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="22" t="s">
         <v>49</v>
       </c>
       <c r="E15" s="20" t="s">
@@ -1619,20 +1695,20 @@
       <c r="F15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="24">
+      <c r="A16" s="21">
         <v>11</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="22" t="s">
         <v>51</v>
       </c>
       <c r="E16" s="20" t="s">
@@ -1641,37 +1717,304 @@
       <c r="F16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
     </row>
     <row r="17" spans="1:8" ht="87" x14ac:dyDescent="0.35">
-      <c r="A17" s="24">
+      <c r="A17" s="21">
         <v>12</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="25"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="23"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+    </row>
+    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>2</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="14"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="23"/>
+      <c r="A19" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="23"/>
+      <c r="A20" s="1">
+        <v>1</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="18"/>
+      <c r="H20" s="19"/>
+    </row>
+    <row r="21" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+      <c r="A21" s="21">
+        <v>2</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+    </row>
+    <row r="22" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+      <c r="A22" s="21">
+        <v>3</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+    </row>
+    <row r="23" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="21">
+        <v>4</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+    </row>
+    <row r="24" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="21">
+        <v>5</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+    </row>
+    <row r="25" spans="1:8" ht="116" x14ac:dyDescent="0.35">
+      <c r="A25" s="21">
+        <v>6</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+    </row>
+    <row r="26" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="21">
+        <v>7</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+    </row>
+    <row r="27" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="21">
+        <v>8</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+    </row>
+    <row r="28" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="21">
+        <v>9</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+    </row>
+    <row r="29" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="21">
+        <v>10</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="26"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1691,7 +2034,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F30" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -1711,16 +2054,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -1878,18 +2221,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1909,18 +2252,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7AAB18-59B2-4688-A91A-8F770B44DA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CC9EC1-BBAA-40B2-85B8-57253F496EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="81">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -268,13 +268,76 @@
   </si>
   <si>
     <t xml:space="preserve"> Hans Ehm, Abdelgafar Ismail, Excellence program Students , Botho Schanze, Tim , Hans ,  Wilfried , Ana….</t>
+  </si>
+  <si>
+    <t>31.07.2026</t>
+  </si>
+  <si>
+    <t>Phares:
+ content well understood – it would be better to use a white color on the blue background
+Irrigation system: Thank you for working on water-saving irrigiation, the link does not work in your homepage
+Next steps: use Miro board to break down your tasks and create a mock-up of your app</t>
+  </si>
+  <si>
+    <t>Esther:
+ all clear - thanks
+Plants: thank you for using Miro to break down your tasks, I gave you feedback in Miro, next step is to execute the steps
+Start with a general mockup like the others and proceed task by task
+Great to use the data base feature
+Regarding putting together the apps – this we didn’t nominate a person yet it we will see based on how fast</t>
+  </si>
+  <si>
+    <t>Rayane: 
+all clear – thanks
+Equipment: your Mockup looksvery good, interactive and different taps
+What I think missing is the equipment utilization in percentage
+The ERD looks good as well, but I would recommend to use a concept like 4M Machine, Method, Material &amp; human
+Question about the stack which will be used to build the app</t>
+  </si>
+  <si>
+    <t>Aida:
+ content well understood – for the hyperlink you can use a clear text like “Energy system”
+Nice to have you in the call this week: please use Miro to break down your tasks
+It is very good to add energy backup &amp; carbon footprint
+Next please create a mock-up</t>
+  </si>
+  <si>
+    <t>Alix:
+ content well understood: – for the hyperlink you can use a clear text like “Visitor Management System” and “Mockup”
+Nice to have you in the call this week:
+Your mock-up looks very good – try to use similar fonts as the other mock-up (all apps need to use same fonts)
+Next step: please use Miro to break down your tasks</t>
+  </si>
+  <si>
+    <t>Christelle:
+ all clear – thanks, maybe you use a better bullte point (not one with a “?” inside the black diamond
+Crops storage: thank you for creating a Mock-up it looks good,
+but please move towards a more interactive version
+Use miro to break down your tasks – start with the first task directly</t>
+  </si>
+  <si>
+    <t>Mariata:
+ all clear – thanks
+Sales &amp; marketing: thank you to work on the challenges, it looks very good
+Next step: Use miro to break down your tasks – start with the first task directly</t>
+  </si>
+  <si>
+    <t>Tania:
+all good maybe remove the “?”
+Face recognition: if possible to translate your pdf into a mockup and use Miro
+Question about the app building: good question, make a plan in Miro and follow it step by step</t>
+  </si>
+  <si>
+    <t>Abdoul:
+Product transform: your Mockup looksvery good, interactive and different taps
+Any possibility to get input from Plants app e.g. amount of Mango harvested, make a forecast based on historical values</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -335,6 +398,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -437,7 +506,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -512,17 +581,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1371,7 +1431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -2006,15 +2066,271 @@
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="26"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
+    <row r="30" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>3</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="14"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
+        <v>1</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="18"/>
+      <c r="H32" s="19"/>
+    </row>
+    <row r="33" spans="1:8" ht="139.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="21">
+        <v>2</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+    </row>
+    <row r="34" spans="1:8" ht="114" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="21">
+        <v>3</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+    </row>
+    <row r="35" spans="1:8" ht="136" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="21">
+        <v>4</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+    </row>
+    <row r="36" spans="1:8" ht="116" x14ac:dyDescent="0.35">
+      <c r="A36" s="21">
+        <v>5</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+    </row>
+    <row r="37" spans="1:8" ht="116" x14ac:dyDescent="0.35">
+      <c r="A37" s="21">
+        <v>6</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+    </row>
+    <row r="38" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="21">
+        <v>7</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+    </row>
+    <row r="39" spans="1:8" ht="97" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="21">
+        <v>8</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+    </row>
+    <row r="40" spans="1:8" ht="116" x14ac:dyDescent="0.35">
+      <c r="A40" s="21">
+        <v>9</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+    </row>
+    <row r="41" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+      <c r="A41" s="21">
+        <v>10</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -2034,7 +2350,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F30" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -2221,18 +2537,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2252,18 +2568,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CC9EC1-BBAA-40B2-85B8-57253F496EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7AB2BD-A4FA-45D4-8BB9-2EACB4433E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="91">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -331,6 +331,90 @@
     <t>Abdoul:
 Product transform: your Mockup looksvery good, interactive and different taps
 Any possibility to get input from Plants app e.g. amount of Mango harvested, make a forecast based on historical values</t>
+  </si>
+  <si>
+    <t>07.08.2026</t>
+  </si>
+  <si>
+    <t>Rayane: thanks for the update. Maybe you can write out the abbreviation like CRUDE
+Feedback from last week:
+Equipment: your Mockup looksvery good, interactive and different taps – I like that you have dashboards and scorecards
+What I think missing is the equipment utilization in percentage – thanks for adding it it looks good now
+The ERD looks good as well, but I would recommend to use a concept like 4M Machine, Method, Material &amp; human – thanks for adding it
+Question about the stack which will be used to build the app – I brought Anar to the call with his computer science he will be available to support your technical questions
+Feedback from this week:
+Please add a tab in your mock-up for what -if scenario analysis – e.g. say we want to add one more equipment what cost and benefits it brings you maybe show there</t>
+  </si>
+  <si>
+    <t>Justine: well understood, good homepage; you have one label in a diamond at Project/Task which is a “?” on our screen. Please try to get it of.
+Feedback from last week: please add your updates to the homepage
+Nice to have you in the call this week: please use Miro to break down your tasks – thank you for adding your tasks in Miro
+It is very good to add energy backup &amp; carbon footprint
+Next please create a mock-up
+Feedback for next week:
+Please add Mock up to the page</t>
+  </si>
+  <si>
+    <t>Carine: well understood, all good
+Feedback from last week:
+Nice to have you in the call this week:
+Your mock-up looks very good – try to use similar fonts as the other mock-up (all apps need to use same fonts) – woow the mock-up looks very good now improved and matching the style
+Next step: please use Miro to break down your tasks
+Feedback for next week:
+Please add to the mock-up a tab related to events e.g. if the farm is hosting an event</t>
+  </si>
+  <si>
+    <t>Christelle; quite well understood; The text could be improved, like no blank before the coma, Now “_in front of a word
+Feedback from last week:
+Crops storage: thank you for creating a Mock-up it looks good,
+but please move towards a more interactive version – woow also significant improvements from last week altought some tabs are not complete- I like that you have dashboards and scorecards
+Use miro to break down your tasks – start with the first task directly – thank you for filling Miro board
+Feedback for next week:
+Please add a tab in your mock-up for what -if scenario analysis – e.g. say we want to add more storage what is cost and benefits
+Good questions: instead of Infineon logo think as a group to make a logo for the farm – for the data use dummy data at the beginning</t>
+  </si>
+  <si>
+    <t>Ben: quite some strange labels on your homepage
+Feedback from last week:
+Product transform: your Mockup look svery good, interactive and different taps – Mock-up style need to match styles of other apps – make it easy later when integrated all as one platform
+Any possibility to get input from Plants app e.g. amount of Mango harvested, make a forecast based on historical values – thank you for looking at the inputs from the other workstreams
+Feedback for next week:
+Identified cross-functional dependencies – best way to show such cross-function dependency is to build a swimlane diagram – please do it for next week</t>
+  </si>
+  <si>
+    <t>Esther: black on blue is difficult to read
+Ester:
+Feedback from last week:
+Plants: thank you for using Miro to break down your tasks, I gave you feedback in Miro, next step is to execute the steps – also gave feedback this week
+Start with a general mockup like the others and proceed task by task – Mock-up looks very good and it is interactive
+Great to use the data base feature
+Regarding putting together the apps – this we didn’t nominate a person yet it we will see based on how fast
+Feedback for next week:
+Built and tested the first working version of the backend – please add what-if scenario e.g. if we want to increase our plants output what are the scenarios</t>
+  </si>
+  <si>
+    <t>Phares: well understood, all good
+Feedback from last week:
+Irrigation system: Thank you for working on water-saving irrigation, the link does not work in your homepage
+Next steps: use Miro board to break down your tasks and create a mock-up of your app – Thank you for adding your tasks in Miro - I gave you feedback in Miro
+Feedback for next week:
+Thank you working on the backend – you are head of the others I would recommend you build a mock-up finalize it within the next weeks</t>
+  </si>
+  <si>
+    <t>Tanial:
+Feedback from last week:
+Face recognition: if possible to translate your pdf into a mockup and use Miro
+Question about the app building: good question, make a plan in Miro and follow it step by step – thank you for filling the miro
+Feedback for next week:
+Couldn’t see your update on the homepage – as next step I would create the mock-up and add it to the homepage like the others</t>
+  </si>
+  <si>
+    <t>Marita; quite some strange labels on your homepage
+Feedback from last week:
+Sales &amp; marketing: thank you to work on the challenges, it looks very good
+Next step: Use miro to break down your tasks – start with the first task directly – thank you for filling Miro
+Feedback for next week:
+I would create a mock-up like the others</t>
   </si>
 </sst>
 </file>
@@ -575,14 +659,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1431,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -1443,16 +1527,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
@@ -2273,7 +2357,7 @@
       <c r="B39" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="24" t="s">
         <v>78</v>
       </c>
       <c r="D39" s="22" t="s">
@@ -2331,6 +2415,272 @@
       </c>
       <c r="G41" s="22"/>
       <c r="H41" s="22"/>
+    </row>
+    <row r="42" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>4</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="14"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="1">
+        <v>1</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="18"/>
+      <c r="H44" s="19"/>
+    </row>
+    <row r="45" spans="1:8" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="21">
+        <v>2</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+    </row>
+    <row r="46" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="21">
+        <v>3</v>
+      </c>
+      <c r="B46" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+    </row>
+    <row r="47" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="21">
+        <v>4</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+    </row>
+    <row r="48" spans="1:8" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="21">
+        <v>5</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+    </row>
+    <row r="49" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="21">
+        <v>6</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+    </row>
+    <row r="50" spans="1:8" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="21">
+        <v>7</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+    </row>
+    <row r="51" spans="1:8" ht="238.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="21">
+        <v>8</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="22"/>
+      <c r="H51" s="22"/>
+    </row>
+    <row r="52" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="21">
+        <v>9</v>
+      </c>
+      <c r="B52" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+    </row>
+    <row r="53" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+      <c r="A53" s="21">
+        <v>10</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -2350,7 +2700,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -2370,16 +2720,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -2537,18 +2887,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2568,18 +2918,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7AB2BD-A4FA-45D4-8BB9-2EACB4433E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E045578-A8DD-434E-A346-C82A037A6CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="102">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -415,6 +415,96 @@
 Next step: Use miro to break down your tasks – start with the first task directly – thank you for filling Miro
 Feedback for next week:
 I would create a mock-up like the others</t>
+  </si>
+  <si>
+    <t>14.08.2026</t>
+  </si>
+  <si>
+    <t>Next week: Final Mock-up presentation:
+In General Thank you for adopting a one logo for all the farm – if not yet please adopt by all
+in General I would recommend all of you to make your update as follows: show what you did this week, which feedback you incorporated from last week, what is the next steps for next week</t>
+  </si>
+  <si>
+    <t>Justine:
+Feedback from last week: please add your updates to the homepage
+Next please create a mock-up – thank you for creating the mock-up
+Please add Mock up to the page
+Feedback for next week:
+The scenario analysis tab would be great to add interactive charts when the scenario changes the chart changes dynamically like Christelle – unfortunately couldn’t hear you today</t>
+  </si>
+  <si>
+    <t>Tania:
+Feedback from last week:
+Face recognition:
+Couldn’t see your update on the homepage – as next step I would create the mock-up and add it to the homepage like the others – thank you for working on the mock-up it looks great
+Feedback for next week:
+Could you implement the mock-up from power point to web interface like the others and use the style of the others – unfortunately could hear you today</t>
+  </si>
+  <si>
+    <t>Christelle:
+all Good thanks
+Feedback from last week:
+Crops storage:
+Use miro to break down your tasks – start with the first task directly – thank you for filling Miro board – I will give you feedback there directly and you will get answer to your email about
+Please add a tab in your mock-up for what -if scenario analysis – e.g. say we want to add more storage what is cost and benefits – the Scenario Analysis option looks good – what is the point at which benefits are more than costs?
+Good questions: instead of Infineon logo think as a group to make a logo for the farm – for the data use dummy data at the beginning – I checked the logo it looks good
+Feedback for next week:
+Could you please write in the homepage you next steps: and whether you need input for the next step and from whom?</t>
+  </si>
+  <si>
+    <t>Mariata:
+all Good thanks
+Feedback from last week:
+Sales &amp; marketing:
+I would create a mock-up like the others – Thank you for creating the Mock-up it looks great – please use the same style like your colleagues and also add scenario analysis to the mock-up
+Feedback for next week:
+The forecasting model looks good: could you incorporate in the mock-up and if possible show always the last three months actual sales and the forecast for the next 12 months</t>
+  </si>
+  <si>
+    <t>Ben:
+all Good thanks
+Feedback from last week:
+Product transform:
+Identified cross-functional dependencies – best way to show such cross-function dependency is to build a swimlane diagram – thank you for showing that
+Feedback for next week:
+What is the next step and please show it always in your homepage and what input you will use for it – Audio as breaking please improve for next time</t>
+  </si>
+  <si>
+    <t>Phares:
+all Good thanks
+Feedback from last week:
+Irrigation system:
+Thank you working on the backend – you are head of the others I would recommend you build a mock-up finalize it within the next weeks – The mock-up looks great please make sure the style is similar to the others
+Feedback for next week:
+Please also create Scenario Analysis</t>
+  </si>
+  <si>
+    <t>Esther:
+all Good thanks
+Feedback from last week:
+Plants:
+Built and tested the first working version of the backend – please add what-if scenario e.g. if we want to increase our plants output what are the scenarios – thank you for adding the scenario Analysis tab (name it as well like that)
+Feedback for next week:
+The scenario Analysis looks good but could you add sliders and dynamic charts like Christelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rayane:
+all Good thanks
+Feedback from last week:
+Equipment:
+Please add a tab in your mock-up for what -if scenario analysis – e.g. say we want to add one more equipment what cost and benefits it brings you maybe show there – looks good please name it scenario analysis and create also sliders and dynamics charts like Christelle
+Feedback from this week:
+For the FE&amp;BE technology questions Anar will provide more information</t>
+  </si>
+  <si>
+    <t>Carine: 
+all Good thanks
+Feedback from last week:
+Nice to have you in the call this week:
+Your mock-up looks very good – try to use similar fonts as the other mock-up (all apps need to use same fonts) – woow the mock-up looks very good now improved and matching the style
+Next step: please use Miro to break down your tasks
+Feedback for next week:
+Please add to the mock-up a tab related to events e.g. if the farm is hosting an event</t>
   </si>
 </sst>
 </file>
@@ -1515,7 +1605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -2681,6 +2771,272 @@
       </c>
       <c r="G53" s="22"/>
       <c r="H53" s="22"/>
+    </row>
+    <row r="54" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A54" s="8">
+        <v>5</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="12"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="14"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A55" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="1">
+        <v>1</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" s="18"/>
+      <c r="H56" s="19"/>
+    </row>
+    <row r="57" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="21">
+        <v>2</v>
+      </c>
+      <c r="B57" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D57" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+    </row>
+    <row r="58" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="21">
+        <v>3</v>
+      </c>
+      <c r="B58" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+    </row>
+    <row r="59" spans="1:8" ht="203" x14ac:dyDescent="0.35">
+      <c r="A59" s="21">
+        <v>4</v>
+      </c>
+      <c r="B59" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+    </row>
+    <row r="60" spans="1:8" ht="290" x14ac:dyDescent="0.35">
+      <c r="A60" s="21">
+        <v>5</v>
+      </c>
+      <c r="B60" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C60" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" s="22"/>
+      <c r="H60" s="22"/>
+    </row>
+    <row r="61" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="21">
+        <v>6</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+    </row>
+    <row r="62" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="21">
+        <v>7</v>
+      </c>
+      <c r="B62" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D62" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+    </row>
+    <row r="63" spans="1:8" ht="163.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="21">
+        <v>8</v>
+      </c>
+      <c r="B63" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D63" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+    </row>
+    <row r="64" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="21">
+        <v>9</v>
+      </c>
+      <c r="B64" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C64" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D64" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" s="22"/>
+      <c r="H64" s="22"/>
+    </row>
+    <row r="65" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+      <c r="A65" s="21">
+        <v>10</v>
+      </c>
+      <c r="B65" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D65" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -2700,7 +3056,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -2887,18 +3243,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2918,18 +3274,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E045578-A8DD-434E-A346-C82A037A6CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062DFFD3-6EB8-40A0-A552-3F5A8B973A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="113">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -505,6 +505,57 @@
 Next step: please use Miro to break down your tasks
 Feedback for next week:
 Please add to the mock-up a tab related to events e.g. if the farm is hosting an event</t>
+  </si>
+  <si>
+    <t>21.08.2026</t>
+  </si>
+  <si>
+    <t>General feedback:
+Mock-up looks very good please proceed to the next steps e.g. BE and database development
+could you have a summary dashboard on top showing the key performance indicators like what Justine showed on top for every category then there are specific tabs for more detailed views
+should we have guidelines for all pages e.g. font size or logo should have white background …etc.</t>
+  </si>
+  <si>
+    <t>Justine: Mock-up looks very good congrats -logo needs to have white background – she presented very good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariata:
+Not in the call </t>
+  </si>
+  <si>
+    <t>Ben:
+thanks for the update on the dashboard; it would be interesting how you came to the data shown here; please also update your homepage of not done yet
+ Mock-up looks very good congrats  Logo is too small and style need to be consistent</t>
+  </si>
+  <si>
+    <t>Phares:
+thanks for the update on the dashboard; it would be interesting how you came to the data shown here; please also update your homepage of not done yet
+ Mock-up looks very good congrats Logo size also need to be appropriate</t>
+  </si>
+  <si>
+    <t>Rayane:
+ thanks for the update on the dashboard; it would be interesting how you came to the data shown here; please also update your homepage of not done yet
+Mock-up looks very good congrats Logo size also need to be appropriate</t>
+  </si>
+  <si>
+    <t>Alix:
+thanks for the update on the dashboard; it would be interesting how you came to the data shown here; please also update your homepage of not done yet
+ Mock-up looks very good congrats - Logo and style need to be consistent consistent e.g. font size is very small compared to the others</t>
+  </si>
+  <si>
+    <t>Christelle:
+thanks for the update on the dashboard; it would be interesting how you came to the data shown here; please also update your homepage of not done yet; on your y-axes what I the 5m (% million, always describe what you have on x- and y-axes)
+ Mock-up looks very good congrats – logo and font size needs to be adjusted it is too small – search functionality/dark theme is very good idea</t>
+  </si>
+  <si>
+    <t>Tania: 
+thanks for the update on the dashboard;
+Mock-up looks very good congrats – please use style from the others, color, font and font size</t>
+  </si>
+  <si>
+    <t>Esther: 
+thanks for the update on the dashboard; it would be interesting how you came to the data shown here; please also update your homepage of not done yet
+Mock-up looks very good congrats - please use style from the others, color, font and font size</t>
   </si>
 </sst>
 </file>
@@ -1605,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -3037,6 +3088,272 @@
       </c>
       <c r="G65" s="22"/>
       <c r="H65" s="22"/>
+    </row>
+    <row r="66" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A66" s="8">
+        <v>6</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="12"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="14"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A67" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="116" x14ac:dyDescent="0.35">
+      <c r="A68" s="1">
+        <v>1</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E68" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" s="18"/>
+      <c r="H68" s="19"/>
+    </row>
+    <row r="69" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="21">
+        <v>2</v>
+      </c>
+      <c r="B69" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C69" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D69" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+    </row>
+    <row r="70" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="21">
+        <v>3</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D70" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+    </row>
+    <row r="71" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="21">
+        <v>4</v>
+      </c>
+      <c r="B71" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C71" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D71" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+    </row>
+    <row r="72" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="21">
+        <v>5</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C72" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D72" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+    </row>
+    <row r="73" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A73" s="21">
+        <v>6</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C73" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D73" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+    </row>
+    <row r="74" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="21">
+        <v>7</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+    </row>
+    <row r="75" spans="1:8" ht="51" x14ac:dyDescent="0.35">
+      <c r="A75" s="21">
+        <v>8</v>
+      </c>
+      <c r="B75" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C75" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D75" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+    </row>
+    <row r="76" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="21">
+        <v>9</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C76" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
+    </row>
+    <row r="77" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A77" s="21">
+        <v>10</v>
+      </c>
+      <c r="B77" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C77" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D77" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -3056,7 +3373,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -3243,18 +3560,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3274,18 +3591,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062DFFD3-6EB8-40A0-A552-3F5A8B973A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55966A5-501D-4205-94BE-362A69654B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="124">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -556,6 +556,84 @@
     <t>Esther: 
 thanks for the update on the dashboard; it would be interesting how you came to the data shown here; please also update your homepage of not done yet
 Mock-up looks very good congrats - please use style from the others, color, font and font size</t>
+  </si>
+  <si>
+    <t>28.08.2026</t>
+  </si>
+  <si>
+    <t>Rayane:
+Feedback from last week:
+Equipment:
+For the FE&amp;BE technology questions Anar will provide more information – thank you for adding KPIs and data sources
+Feedback from this week:
+What is a machine registry – will you use machine learning for optimization of equipment?</t>
+  </si>
+  <si>
+    <t>Justine:
+Feedback from last week: please add your updates to the homepage
+The scenario analysis tab would be great to add interactive charts when the scenario changes the chart changes dynamically like Christelle – unfortunately couldn’t hear you today
+Feedback for next week:
+Thank you for correcting the logo
+Well explained your BE progress – just ensure before developing the FE that mock-up is consistent with all</t>
+  </si>
+  <si>
+    <t>Carine:
+Feedback from last week:
+Would it be possible to use the visitor management app as a marketing tool, it will give input to the sales and marketing platform of potential customers – e.g. a questionaries about the reason for the visit and if you spot a potential customer give this feedback to the sales and marketing team to initiate contact
+Feedback for next week:
+Thank you for fixing the logo and font style – for the database if you have questions address them to Anar</t>
+  </si>
+  <si>
+    <t>Christelle:
+Feedback from last week:
+Crops storage:
+Could you please write in the homepage you next steps: and whether you need input for the next step and from whom?
+Feedback for next week:
+Thank you for addressing the feedback from us – for the BE and database</t>
+  </si>
+  <si>
+    <t>Mariata:
+Feedback from last week:
+Sales &amp; marketing:
+The forecasting model looks good: could you incorporate in the mock-up and if possible show always the last three months actual sales and the forecast for the next 12 months
+Feedback for next week:
+Thank you for reworking on the mock-up please finalize it this week and move to the BE part</t>
+  </si>
+  <si>
+    <t>Tania:
+Feedback from last week:
+Face recognition:
+Could you implement the mock-up from power point to web interface like the others and use the style of the others – unfortunately could hear you today
+Feedback for next week:
+Thank you for implementing the feedback from us – moving to the FE and BE is a good step – approach Anar if you have questions</t>
+  </si>
+  <si>
+    <t>Ben:
+Feedback from last week:
+Product transform:
+What is the next step and please show it always in your homepage and what input you will use for it – Audio as breaking please improve for next time
+Feedback for next week:
+Good progress, you already in FE Integration which means you already finished FE and BE and Database?</t>
+  </si>
+  <si>
+    <t>Ester:
+Feedback from last week:
+Plants:
+The scenario Analysis looks good but could you add sliders and dynamic charts like Christelle
+Feedback for next week:
+Thank you for implementing the feedback – could you repeat your question</t>
+  </si>
+  <si>
+    <t>Phares:
+Feedback from last week:
+Irrigation system:
+Please also create Scenario Analysis
+Feedback for next week:
+Thank you for working on the feedback – your next step check if you add a Scenario Analysis</t>
+  </si>
+  <si>
+    <t>General feedback: share best practices and lessons learned when you learn something
+For any question regarding the stacks please reach out to Anar:Anar.Akhmedov@infineon.com</t>
   </si>
 </sst>
 </file>
@@ -1656,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -3354,6 +3432,272 @@
       </c>
       <c r="G77" s="22"/>
       <c r="H77" s="22"/>
+    </row>
+    <row r="78" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A78" s="8">
+        <v>7</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D78" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="12"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="14"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A79" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A80" s="1">
+        <v>1</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" s="18"/>
+      <c r="H80" s="19"/>
+    </row>
+    <row r="81" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A81" s="21">
+        <v>2</v>
+      </c>
+      <c r="B81" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D81" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" s="22"/>
+      <c r="H81" s="22"/>
+    </row>
+    <row r="82" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+      <c r="A82" s="21">
+        <v>3</v>
+      </c>
+      <c r="B82" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C82" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D82" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" s="22"/>
+      <c r="H82" s="22"/>
+    </row>
+    <row r="83" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A83" s="21">
+        <v>4</v>
+      </c>
+      <c r="B83" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C83" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D83" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" s="22"/>
+      <c r="H83" s="22"/>
+    </row>
+    <row r="84" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A84" s="21">
+        <v>5</v>
+      </c>
+      <c r="B84" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C84" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D84" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" s="22"/>
+      <c r="H84" s="22"/>
+    </row>
+    <row r="85" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+      <c r="A85" s="21">
+        <v>6</v>
+      </c>
+      <c r="B85" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C85" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D85" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" s="22"/>
+      <c r="H85" s="22"/>
+    </row>
+    <row r="86" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+      <c r="A86" s="21">
+        <v>7</v>
+      </c>
+      <c r="B86" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C86" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D86" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" s="22"/>
+      <c r="H86" s="22"/>
+    </row>
+    <row r="87" spans="1:8" ht="151" x14ac:dyDescent="0.35">
+      <c r="A87" s="21">
+        <v>8</v>
+      </c>
+      <c r="B87" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C87" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D87" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" s="22"/>
+      <c r="H87" s="22"/>
+    </row>
+    <row r="88" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A88" s="21">
+        <v>9</v>
+      </c>
+      <c r="B88" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C88" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D88" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" s="22"/>
+      <c r="H88" s="22"/>
+    </row>
+    <row r="89" spans="1:8" ht="145" x14ac:dyDescent="0.35">
+      <c r="A89" s="21">
+        <v>10</v>
+      </c>
+      <c r="B89" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C89" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D89" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" s="22"/>
+      <c r="H89" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -3373,7 +3717,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -3560,18 +3904,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3591,18 +3935,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>